--- a/artfynd/A 31113-2025 artfynd.xlsx
+++ b/artfynd/A 31113-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160237</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102379918</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80787425</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121850577</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2310264</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102379912</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1393,6 +1428,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3601886</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4538614</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,6 +1637,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80787424</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1685,8 +1735,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5994136</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31113-2025 artfynd.xlsx
+++ b/artfynd/A 31113-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121850577</v>
+        <v>136041196</v>
       </c>
       <c r="B5" t="n">
-        <v>57132</v>
+        <v>96504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,45 +1016,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stackmyran, Mpd</t>
+          <t>Stackmyran, Stackmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536846</v>
+        <v>536839</v>
       </c>
       <c r="R5" t="n">
-        <v>6940043</v>
+        <v>6940081</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,22 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,27 +1090,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tobias Ljungquist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tobias Ljungquist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121850577</t>
+          <t>https://artportalen.se/Sighting/136041196</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2310264</v>
+        <v>136041562</v>
       </c>
       <c r="B6" t="n">
-        <v>99142</v>
+        <v>91834</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,37 +1118,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Längs E14 "Långsyna", Mpd</t>
+          <t>Stackmyran, Stackmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536891</v>
+        <v>536920</v>
       </c>
       <c r="R6" t="n">
-        <v>6940002</v>
+        <v>6939997</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,12 +1172,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2009-06-30</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2009-06-30</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,69 +1192,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Margareta Edqvist, Mora Aronsson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2310264</t>
+          <t>https://artportalen.se/Sighting/136041562</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102379912</v>
+        <v>136041712</v>
       </c>
       <c r="B7" t="n">
-        <v>98030</v>
+        <v>89276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221063</v>
+        <v>4404</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norr om Ensillre, E14, vägkant, Mpd</t>
+          <t>Stackmyran, Stackmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536841</v>
+        <v>536939</v>
       </c>
       <c r="R7" t="n">
-        <v>6940059</v>
+        <v>6939977</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,72 +1288,79 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102379912</t>
+          <t>https://artportalen.se/Sighting/136041712</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3601886</v>
+        <v>121850577</v>
       </c>
       <c r="B8" t="n">
-        <v>102464</v>
+        <v>57132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221343</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Längs E14 "Långsyna", Mpd</t>
+          <t>Stackmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536891</v>
+        <v>536846</v>
       </c>
       <c r="R8" t="n">
-        <v>6940002</v>
+        <v>6940043</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,12 +1384,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2009-06-30</t>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2009-06-30</t>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,27 +1414,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Tobias Ljungquist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Margareta Edqvist, Mora Aronsson</t>
+          <t>Tobias Ljungquist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3601886</t>
+          <t>https://artportalen.se/Sighting/121850577</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4538614</v>
+        <v>136041092</v>
       </c>
       <c r="B9" t="n">
-        <v>98050</v>
+        <v>58143</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,37 +1442,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222112</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Längs E14 "Långsyna", Mpd</t>
+          <t>Stackmyran, Stackmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536891</v>
+        <v>536849</v>
       </c>
       <c r="R9" t="n">
-        <v>6940002</v>
+        <v>6940119</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,12 +1496,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2009-06-30</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2009-06-30</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,27 +1516,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Margareta Edqvist, Mora Aronsson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4538614</t>
+          <t>https://artportalen.se/Sighting/136041092</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80787424</v>
+        <v>2310264</v>
       </c>
       <c r="B10" t="n">
-        <v>98137</v>
+        <v>99142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,37 +1544,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222741</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ensillre kalkbarrskog, NV om naturreservatet, S om väg, Mpd</t>
+          <t>Längs E14 "Långsyna", Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536938</v>
+        <v>536891</v>
       </c>
       <c r="R10" t="n">
-        <v>6940035</v>
+        <v>6940002</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1603,12 +1598,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-09-02</t>
+          <t>2009-06-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-09-02</t>
+          <t>2009-06-30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1619,36 +1614,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>gammal barrsumpskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Margareta Edqvist, Mora Aronsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80787424</t>
+          <t>https://artportalen.se/Sighting/2310264</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5994136</v>
+        <v>136042167</v>
       </c>
       <c r="B11" t="n">
-        <v>99121</v>
+        <v>99630</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,33 +1646,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223614</v>
+        <v>219880</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig brudsporre</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. conopsea</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Längs E14 "Långsyna", Mpd</t>
+          <t>Stackmyran, Stackmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536891</v>
+        <v>536978</v>
       </c>
       <c r="R11" t="n">
-        <v>6940002</v>
+        <v>6939939</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1706,12 +1700,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2009-06-30</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2009-06-30</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1726,16 +1720,736 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Margareta Edqvist, Mora Aronsson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136042167</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>102379912</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98030</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norr om Ensillre, E14, vägkant, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>536841</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6940059</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102379912</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136041541</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98201</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stackmyran, Stackmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>536919</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6940003</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136041541</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3601886</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Längs E14 "Långsyna", Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>536891</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6940002</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2009-06-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2009-06-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist, Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3601886</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4538614</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Längs E14 "Långsyna", Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>536891</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6940002</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2009-06-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2009-06-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist, Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4538614</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>80787424</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ensillre kalkbarrskog, NV om naturreservatet, S om väg, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>536938</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6940035</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2019-09-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2019-09-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>gammal barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80787424</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136041496</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99569</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stackmyran, Stackmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>536911</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6940023</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136041496</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5994136</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99121</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223614</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vanlig brudsporre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Längs E14 "Långsyna", Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>536891</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6940002</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2009-06-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2009-06-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist, Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/5994136</t>
         </is>
@@ -1753,6 +2467,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31113-2025 artfynd.xlsx
+++ b/artfynd/A 31113-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>136041196</v>
       </c>
       <c r="B5" t="n">
-        <v>96504</v>
+        <v>96505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136042167</v>
       </c>
       <c r="B11" t="n">
-        <v>99630</v>
+        <v>99631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136041541</v>
       </c>
       <c r="B13" t="n">
-        <v>98201</v>
+        <v>98202</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136041496</v>
       </c>
       <c r="B17" t="n">
-        <v>99569</v>
+        <v>99570</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31113-2025 artfynd.xlsx
+++ b/artfynd/A 31113-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>136041196</v>
       </c>
       <c r="B5" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136041562</v>
       </c>
       <c r="B6" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136041712</v>
       </c>
       <c r="B7" t="n">
-        <v>89276</v>
+        <v>89277</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136042167</v>
       </c>
       <c r="B11" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136041541</v>
       </c>
       <c r="B13" t="n">
-        <v>98202</v>
+        <v>98203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136041496</v>
       </c>
       <c r="B17" t="n">
-        <v>99570</v>
+        <v>99571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31113-2025 artfynd.xlsx
+++ b/artfynd/A 31113-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>136041196</v>
       </c>
       <c r="B5" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136041562</v>
       </c>
       <c r="B6" t="n">
-        <v>91835</v>
+        <v>91836</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136041712</v>
       </c>
       <c r="B7" t="n">
-        <v>89277</v>
+        <v>89278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136042167</v>
       </c>
       <c r="B11" t="n">
-        <v>99632</v>
+        <v>99633</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136041541</v>
       </c>
       <c r="B13" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136041496</v>
       </c>
       <c r="B17" t="n">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31113-2025 artfynd.xlsx
+++ b/artfynd/A 31113-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>136041196</v>
       </c>
       <c r="B5" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136041562</v>
       </c>
       <c r="B6" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136041712</v>
       </c>
       <c r="B7" t="n">
-        <v>89278</v>
+        <v>89279</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136041092</v>
       </c>
       <c r="B9" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136042167</v>
       </c>
       <c r="B11" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136041541</v>
       </c>
       <c r="B13" t="n">
-        <v>98204</v>
+        <v>98205</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136041496</v>
       </c>
       <c r="B17" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31113-2025 artfynd.xlsx
+++ b/artfynd/A 31113-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>136041196</v>
       </c>
       <c r="B5" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136041562</v>
       </c>
       <c r="B6" t="n">
-        <v>91837</v>
+        <v>91843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136041712</v>
       </c>
       <c r="B7" t="n">
-        <v>89279</v>
+        <v>89285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136041092</v>
       </c>
       <c r="B9" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136042167</v>
       </c>
       <c r="B11" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136041541</v>
       </c>
       <c r="B13" t="n">
-        <v>98205</v>
+        <v>98211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136041496</v>
       </c>
       <c r="B17" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31113-2025 artfynd.xlsx
+++ b/artfynd/A 31113-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>136041196</v>
       </c>
       <c r="B5" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136041562</v>
       </c>
       <c r="B6" t="n">
-        <v>91843</v>
+        <v>91844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136041712</v>
       </c>
       <c r="B7" t="n">
-        <v>89285</v>
+        <v>89286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136041092</v>
       </c>
       <c r="B9" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136042167</v>
       </c>
       <c r="B11" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136041541</v>
       </c>
       <c r="B13" t="n">
-        <v>98211</v>
+        <v>98212</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136041496</v>
       </c>
       <c r="B17" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31113-2025 artfynd.xlsx
+++ b/artfynd/A 31113-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>136041196</v>
       </c>
       <c r="B5" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136041562</v>
       </c>
       <c r="B6" t="n">
-        <v>91844</v>
+        <v>91850</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136041712</v>
       </c>
       <c r="B7" t="n">
-        <v>89286</v>
+        <v>89292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136042167</v>
       </c>
       <c r="B11" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136041541</v>
       </c>
       <c r="B13" t="n">
-        <v>98212</v>
+        <v>98223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136041496</v>
       </c>
       <c r="B17" t="n">
-        <v>99580</v>
+        <v>99591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31113-2025 artfynd.xlsx
+++ b/artfynd/A 31113-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>136041196</v>
       </c>
       <c r="B5" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136041562</v>
       </c>
       <c r="B6" t="n">
-        <v>91850</v>
+        <v>91857</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136041712</v>
       </c>
       <c r="B7" t="n">
-        <v>89292</v>
+        <v>89299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136041092</v>
       </c>
       <c r="B9" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136042167</v>
       </c>
       <c r="B11" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136041541</v>
       </c>
       <c r="B13" t="n">
-        <v>98223</v>
+        <v>98236</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136041496</v>
       </c>
       <c r="B17" t="n">
-        <v>99591</v>
+        <v>99604</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31113-2025 artfynd.xlsx
+++ b/artfynd/A 31113-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>136041196</v>
       </c>
       <c r="B5" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136041562</v>
       </c>
       <c r="B6" t="n">
-        <v>91857</v>
+        <v>91858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136041712</v>
       </c>
       <c r="B7" t="n">
-        <v>89299</v>
+        <v>89300</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136042167</v>
       </c>
       <c r="B11" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136041541</v>
       </c>
       <c r="B13" t="n">
-        <v>98236</v>
+        <v>98237</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136041496</v>
       </c>
       <c r="B17" t="n">
-        <v>99604</v>
+        <v>99605</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31113-2025 artfynd.xlsx
+++ b/artfynd/A 31113-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>136041196</v>
       </c>
       <c r="B5" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136041562</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>91871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136041712</v>
       </c>
       <c r="B7" t="n">
-        <v>89300</v>
+        <v>89313</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136041092</v>
       </c>
       <c r="B9" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136042167</v>
       </c>
       <c r="B11" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136041541</v>
       </c>
       <c r="B13" t="n">
-        <v>98237</v>
+        <v>98250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136041496</v>
       </c>
       <c r="B17" t="n">
-        <v>99605</v>
+        <v>99618</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31113-2025 artfynd.xlsx
+++ b/artfynd/A 31113-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>136041196</v>
       </c>
       <c r="B5" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136041562</v>
       </c>
       <c r="B6" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136041712</v>
       </c>
       <c r="B7" t="n">
-        <v>89313</v>
+        <v>89314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136042167</v>
       </c>
       <c r="B11" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136041541</v>
       </c>
       <c r="B13" t="n">
-        <v>98250</v>
+        <v>98251</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>136041496</v>
       </c>
       <c r="B17" t="n">
-        <v>99618</v>
+        <v>99619</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
